--- a/data/trans_bre/IP19C05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,35</t>
+          <t>0,0; 9,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 8,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,92</t>
+          <t>0,0; 10,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,59</t>
+          <t>-2,17; 0,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,45</t>
+          <t>-2,02; 2,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,53</t>
+          <t>-0,97; 3,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 302,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,85; 350,55</t>
+          <t>-85,31; 295,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 467,1</t>
+          <t>-48,54; 522,33</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,99</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 7,34</t>
+          <t>-2,64; 7,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 2,2</t>
+          <t>-4,75; 2,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,95; 769,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,13</t>
+          <t>-1,22; 1,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,9</t>
+          <t>-0,74; 2,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,59</t>
+          <t>-0,91; 2,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-81,22; 309,13</t>
+          <t>-79,37; 404,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 396,35</t>
+          <t>-37,13; 299,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 297,13</t>
+          <t>-38,44; 320,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,28</t>
+          <t>0,0; 9,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,12</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,69</t>
+          <t>0,0; 13,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,87</t>
+          <t>-2,3; 0,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,12</t>
+          <t>-1,87; 2,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,59</t>
+          <t>-1,16; 3,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 302,99</t>
+          <t>-100,0; 304,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,31; 295,74</t>
+          <t>-78,91; 332,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 522,33</t>
+          <t>-62,55; 448,7</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 7,08</t>
+          <t>-1,95; 7,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 2,06</t>
+          <t>-4,6; 2,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,95; 769,3</t>
+          <t>-64,65; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,27</t>
+          <t>-1,18; 1,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,74</t>
+          <t>-0,79; 2,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,7</t>
+          <t>-0,93; 2,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,37; 404,08</t>
+          <t>-81,02; 379,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 299,11</t>
+          <t>-39,77; 258,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 320,9</t>
+          <t>-41,91; 242,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,82</t>
+          <t>0,0; 10,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>0,0; 10,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,85</t>
+          <t>-2,63; 0,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,2</t>
+          <t>-1,88; 2,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,38</t>
+          <t>-0,94; 3,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 304,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,91; 332,9</t>
+          <t>-78,85; 350,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,55; 448,7</t>
+          <t>-45,24; 467,1</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 4,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 7,98</t>
+          <t>-2,41; 7,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 2,04</t>
+          <t>-4,88; 2,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,65; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,22</t>
+          <t>-1,24; 1,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,75</t>
+          <t>-0,74; 2,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,58</t>
+          <t>-0,79; 2,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-81,02; 379,39</t>
+          <t>-81,22; 309,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 258,1</t>
+          <t>-35,86; 396,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 242,58</t>
+          <t>-38,01; 297,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,28 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,86</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,64</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>1.859691022835246</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.637500154133211</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.547806256736926</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +632,124 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,35</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,27</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,92</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.34591735858111</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.266358018667962</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.91606602964417</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-42,66%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>77,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 0,59</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,88; 2,45</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,94; 3,53</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-78,85; 350,55</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-45,24; 467,1</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.613091157280883</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.07312764656124057</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.250058821026309</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.4265730734214987</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.04311031966809154</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.7766521923782659</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,22</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-37,33%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.634999167172007</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.883161733768069</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.9431921475033266</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-0.7884781723897816</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.452403862190932</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,99</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,41; 7,34</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,88; 2,2</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5903479029916311</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.446205942282257</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.529808369097302</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>3.505487477805314</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4.670977104941629</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +757,151 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,16%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,17%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.8352988376442547</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.220643352075801</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.8912657302152291</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.8557134628267135</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3733072289562075</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,24; 1,13</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,74; 2,9</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,79; 2,59</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-81,22; 309,13</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-35,86; 396,35</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-38,01; 297,13</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.407336619697742</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.876049764413351</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.987041556367487</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.342058163255835</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.199943257189137</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.01129055055764383</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9243879343079033</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8388304965545604</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.01156439558567262</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.5441273032485812</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.5017371236590873</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.236873151634271</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.7366684071880731</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.7905734161701663</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.8122246853555277</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3585518719476887</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3800751984856841</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.125210289242748</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.904313393394856</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.589864854486734</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>3.091292136617253</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>3.963457609350142</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.971283089795334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +910,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
